--- a/Models/Model Outputs/DWLW_elpd_waic_Formatted.xlsx
+++ b/Models/Model Outputs/DWLW_elpd_waic_Formatted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarahjennings/Desktop/MAPS-Phenology-Project/Models/Model Outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{11B4546F-0E2F-3D4C-AF54-19E0F39E5835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7721172B-0215-274C-AEA1-36D283502154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="37780" yWindow="-2200" windowWidth="26840" windowHeight="15440" xr2:uid="{FA2B6CEF-C2CC-7C4B-AD7D-A8FF66379676}"/>
   </bookViews>
@@ -245,7 +245,265 @@
   </si>
   <si>
     <r>
-      <t>Lincoln sparrow (</t>
+      <t>MacGillivray's warbler (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Geothlypis tolmiei</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Northern cardinal (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cardinalis cardinalis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Oregon junco (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Junco hyemalis oreganus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ovenbird (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Seiurus aurocapilla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Song sparrow (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Melospiza melodia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Swainson's thrush (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Catharus ustulatus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tufted titmouse (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Baeolophus bicolor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Wilson's warbler (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Cardellina pusilla</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Wood thrush (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Hylocichla mustelina</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Yellow warbler (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Setophaga petechia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>ELPD Difference</t>
+  </si>
+  <si>
+    <t>SE of ELPD Difference</t>
+  </si>
+  <si>
+    <t>wAIC Difference</t>
+  </si>
+  <si>
+    <t>Long-term</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <r>
+      <t>Lincoln's sparrow (</t>
     </r>
     <r>
       <rPr>
@@ -266,264 +524,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>MacGillivray's warbler (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Geothlypis tolmiei</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Northern cardinal (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cardinalis cardinalis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Oregon junco (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Junco hyemalis oreganus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Ovenbird (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Seiurus aurocapilla</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Song sparrow (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Melospiza melodia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Swainson's thrush (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Catharus ustulatus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Tufted titmouse (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Baeolophus bicolor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Wilson's warbler (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cardellina pusilla</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Wood thrush (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Hylocichla mustelina</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Yellow warbler (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Setophaga petechia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Species</t>
-  </si>
-  <si>
-    <t>ELPD Difference</t>
-  </si>
-  <si>
-    <t>SE of ELPD Difference</t>
-  </si>
-  <si>
-    <t>wAIC Difference</t>
-  </si>
-  <si>
-    <t>Long-term</t>
-  </si>
-  <si>
-    <t>Decision</t>
   </si>
 </sst>
 </file>
@@ -1047,18 +1047,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1454,24 +1449,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3">
@@ -1484,7 +1479,7 @@
         <v>8.1479999999999997</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -1609,7 +1604,7 @@
     </row>
     <row r="11" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3">
         <v>-3.5489999999999999</v>
@@ -1624,7 +1619,7 @@
     </row>
     <row r="12" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <v>-2.488</v>
@@ -1639,7 +1634,7 @@
     </row>
     <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>-1.034</v>
@@ -1654,7 +1649,7 @@
     </row>
     <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
         <v>-6.9779999999999998</v>
@@ -1666,12 +1661,12 @@
         <v>13.878</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3">
         <v>-0.25600000000000001</v>
@@ -1686,7 +1681,7 @@
     </row>
     <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
         <v>-5.63</v>
@@ -1698,12 +1693,12 @@
         <v>10.91</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>-0.23100000000000001</v>
@@ -1718,7 +1713,7 @@
     </row>
     <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
         <v>-0.88700000000000001</v>
@@ -1733,7 +1728,7 @@
     </row>
     <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
         <v>-1.6279999999999999</v>
@@ -1747,34 +1742,34 @@
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3">
+        <v>-1.9890000000000001</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1.427</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.9159999999999999</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="5">
-        <v>-1.9890000000000001</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1.427</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2.9159999999999999</v>
-      </c>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="B21" s="5">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="5">
         <v>1.9770000000000001</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="5">
         <v>2.0819999999999999</v>
       </c>
-      <c r="E21" s="9"/>
+      <c r="E21" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{09A3DEE4-77F3-2F4C-8E36-9E053418D5D6}">
